--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -1723,10 +1723,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119839518</v>
+        <v>119839513</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,25 +1735,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547209</v>
+        <v>547275</v>
       </c>
       <c r="R12" t="n">
-        <v>6960619</v>
+        <v>6960558</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119839513</v>
+        <v>119839518</v>
       </c>
       <c r="B13" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,25 +1837,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547275</v>
+        <v>547209</v>
       </c>
       <c r="R13" t="n">
-        <v>6960558</v>
+        <v>6960619</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2437,10 +2437,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839529</v>
+        <v>119839519</v>
       </c>
       <c r="B19" t="n">
-        <v>91310</v>
+        <v>91840</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,25 +2449,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547537</v>
+        <v>547233</v>
       </c>
       <c r="R19" t="n">
-        <v>6960720</v>
+        <v>6960631</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839519</v>
+        <v>119839529</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>91310</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2551,25 +2551,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547233</v>
+        <v>547537</v>
       </c>
       <c r="R20" t="n">
-        <v>6960631</v>
+        <v>6960720</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -1723,10 +1723,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119839513</v>
+        <v>119839516</v>
       </c>
       <c r="B12" t="n">
-        <v>91832</v>
+        <v>91310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,25 +1735,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>1958</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547275</v>
+        <v>547148</v>
       </c>
       <c r="R12" t="n">
-        <v>6960558</v>
+        <v>6960637</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119839518</v>
+        <v>119839512</v>
       </c>
       <c r="B13" t="n">
-        <v>91840</v>
+        <v>91825</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,25 +1837,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>1968</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547209</v>
+        <v>547281</v>
       </c>
       <c r="R13" t="n">
-        <v>6960619</v>
+        <v>6960553</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1927,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119839524</v>
+        <v>119839531</v>
       </c>
       <c r="B14" t="n">
-        <v>91856</v>
+        <v>91852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,25 +1939,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547492</v>
+        <v>547405</v>
       </c>
       <c r="R14" t="n">
-        <v>6960705</v>
+        <v>6960663</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2029,10 +2029,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119839525</v>
+        <v>119839529</v>
       </c>
       <c r="B15" t="n">
-        <v>91463</v>
+        <v>91310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2041,25 +2041,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4745</v>
+        <v>1958</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547520</v>
+        <v>547537</v>
       </c>
       <c r="R15" t="n">
-        <v>6960746</v>
+        <v>6960720</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119839531</v>
+        <v>119839527</v>
       </c>
       <c r="B16" t="n">
-        <v>91852</v>
+        <v>91826</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2143,25 +2143,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>3100</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547405</v>
+        <v>547533</v>
       </c>
       <c r="R16" t="n">
-        <v>6960663</v>
+        <v>6960760</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2233,10 +2233,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119839522</v>
+        <v>119839517</v>
       </c>
       <c r="B17" t="n">
-        <v>91883</v>
+        <v>91834</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2249,21 +2249,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547502</v>
+        <v>547152</v>
       </c>
       <c r="R17" t="n">
-        <v>6960695</v>
+        <v>6960633</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119839527</v>
+        <v>119839525</v>
       </c>
       <c r="B18" t="n">
-        <v>91826</v>
+        <v>91463</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2351,21 +2351,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3100</v>
+        <v>4745</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547533</v>
+        <v>547520</v>
       </c>
       <c r="R18" t="n">
-        <v>6960760</v>
+        <v>6960746</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2437,10 +2437,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839519</v>
+        <v>119839514</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,25 +2449,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547233</v>
+        <v>547173</v>
       </c>
       <c r="R19" t="n">
-        <v>6960631</v>
+        <v>6960564</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839529</v>
+        <v>119839530</v>
       </c>
       <c r="B20" t="n">
-        <v>91310</v>
+        <v>90087</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2555,21 +2555,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1958</v>
+        <v>256335</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547537</v>
+        <v>547413</v>
       </c>
       <c r="R20" t="n">
-        <v>6960720</v>
+        <v>6960666</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2623,6 +2623,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2641,10 +2642,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119839515</v>
+        <v>119839522</v>
       </c>
       <c r="B21" t="n">
-        <v>91834</v>
+        <v>91883</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2657,21 +2658,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,10 +2682,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547120</v>
+        <v>547502</v>
       </c>
       <c r="R21" t="n">
-        <v>6960622</v>
+        <v>6960695</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2743,10 +2744,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119839528</v>
+        <v>119839526</v>
       </c>
       <c r="B22" t="n">
-        <v>91884</v>
+        <v>91844</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2755,25 +2756,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2783,10 +2784,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547565</v>
+        <v>547529</v>
       </c>
       <c r="R22" t="n">
-        <v>6960801</v>
+        <v>6960749</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2845,10 +2846,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119839530</v>
+        <v>119839528</v>
       </c>
       <c r="B23" t="n">
-        <v>90087</v>
+        <v>91884</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2857,25 +2858,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>256335</v>
+        <v>5449</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2885,10 +2886,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547413</v>
+        <v>547565</v>
       </c>
       <c r="R23" t="n">
-        <v>6960666</v>
+        <v>6960801</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2929,7 +2930,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2948,10 +2948,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119839512</v>
+        <v>119839515</v>
       </c>
       <c r="B24" t="n">
-        <v>91825</v>
+        <v>91834</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2964,21 +2964,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1968</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547281</v>
+        <v>547120</v>
       </c>
       <c r="R24" t="n">
-        <v>6960553</v>
+        <v>6960622</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119839526</v>
+        <v>119839513</v>
       </c>
       <c r="B25" t="n">
-        <v>91844</v>
+        <v>91832</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3062,25 +3062,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547529</v>
+        <v>547275</v>
       </c>
       <c r="R25" t="n">
-        <v>6960749</v>
+        <v>6960558</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3152,10 +3152,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119839516</v>
+        <v>119839524</v>
       </c>
       <c r="B26" t="n">
-        <v>91310</v>
+        <v>91856</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3164,25 +3164,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1958</v>
+        <v>2059</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547148</v>
+        <v>547492</v>
       </c>
       <c r="R26" t="n">
-        <v>6960637</v>
+        <v>6960705</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3254,10 +3254,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119839514</v>
+        <v>119839518</v>
       </c>
       <c r="B27" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3266,25 +3266,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>547173</v>
+        <v>547209</v>
       </c>
       <c r="R27" t="n">
-        <v>6960564</v>
+        <v>6960619</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119839517</v>
+        <v>119839519</v>
       </c>
       <c r="B28" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3368,25 +3368,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>547152</v>
+        <v>547233</v>
       </c>
       <c r="R28" t="n">
-        <v>6960633</v>
+        <v>6960631</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2642,10 +2642,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119839522</v>
+        <v>119839526</v>
       </c>
       <c r="B21" t="n">
-        <v>91883</v>
+        <v>91844</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2654,25 +2654,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5448</v>
+        <v>4365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547502</v>
+        <v>547529</v>
       </c>
       <c r="R21" t="n">
-        <v>6960695</v>
+        <v>6960749</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2744,10 +2744,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119839526</v>
+        <v>119839522</v>
       </c>
       <c r="B22" t="n">
-        <v>91844</v>
+        <v>91883</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2756,25 +2756,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4365</v>
+        <v>5448</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547529</v>
+        <v>547502</v>
       </c>
       <c r="R22" t="n">
-        <v>6960749</v>
+        <v>6960695</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -1723,10 +1723,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119839516</v>
+        <v>119839531</v>
       </c>
       <c r="B12" t="n">
-        <v>91310</v>
+        <v>91852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,25 +1735,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1958</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547148</v>
+        <v>547405</v>
       </c>
       <c r="R12" t="n">
-        <v>6960637</v>
+        <v>6960663</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119839512</v>
+        <v>119839513</v>
       </c>
       <c r="B13" t="n">
-        <v>91825</v>
+        <v>91832</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1841,21 +1841,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1968</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547281</v>
+        <v>547275</v>
       </c>
       <c r="R13" t="n">
-        <v>6960553</v>
+        <v>6960558</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1927,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119839531</v>
+        <v>119839528</v>
       </c>
       <c r="B14" t="n">
-        <v>91852</v>
+        <v>91884</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,25 +1939,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547405</v>
+        <v>547565</v>
       </c>
       <c r="R14" t="n">
-        <v>6960663</v>
+        <v>6960801</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2029,7 +2029,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119839529</v>
+        <v>119839516</v>
       </c>
       <c r="B15" t="n">
         <v>91310</v>
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547537</v>
+        <v>547148</v>
       </c>
       <c r="R15" t="n">
-        <v>6960720</v>
+        <v>6960637</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119839527</v>
+        <v>119839512</v>
       </c>
       <c r="B16" t="n">
-        <v>91826</v>
+        <v>91825</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3100</v>
+        <v>1968</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547533</v>
+        <v>547281</v>
       </c>
       <c r="R16" t="n">
-        <v>6960760</v>
+        <v>6960553</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2233,10 +2233,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119839517</v>
+        <v>119839518</v>
       </c>
       <c r="B17" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2245,25 +2245,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547152</v>
+        <v>547209</v>
       </c>
       <c r="R17" t="n">
-        <v>6960633</v>
+        <v>6960619</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119839525</v>
+        <v>119839522</v>
       </c>
       <c r="B18" t="n">
-        <v>91463</v>
+        <v>91883</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2351,21 +2351,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4745</v>
+        <v>5448</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547520</v>
+        <v>547502</v>
       </c>
       <c r="R18" t="n">
-        <v>6960746</v>
+        <v>6960695</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2437,10 +2437,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839514</v>
+        <v>119839517</v>
       </c>
       <c r="B19" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2453,21 +2453,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547173</v>
+        <v>547152</v>
       </c>
       <c r="R19" t="n">
-        <v>6960564</v>
+        <v>6960633</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839530</v>
+        <v>119839527</v>
       </c>
       <c r="B20" t="n">
-        <v>90087</v>
+        <v>91826</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2551,25 +2551,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>256335</v>
+        <v>3100</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547413</v>
+        <v>547533</v>
       </c>
       <c r="R20" t="n">
-        <v>6960666</v>
+        <v>6960760</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2623,7 +2623,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2642,10 +2641,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119839526</v>
+        <v>119839514</v>
       </c>
       <c r="B21" t="n">
-        <v>91844</v>
+        <v>91884</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2654,25 +2653,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2682,10 +2681,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547529</v>
+        <v>547173</v>
       </c>
       <c r="R21" t="n">
-        <v>6960749</v>
+        <v>6960564</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2744,10 +2743,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119839522</v>
+        <v>119839515</v>
       </c>
       <c r="B22" t="n">
-        <v>91883</v>
+        <v>91834</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2760,21 +2759,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2784,10 +2783,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547502</v>
+        <v>547120</v>
       </c>
       <c r="R22" t="n">
-        <v>6960695</v>
+        <v>6960622</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2846,10 +2845,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119839528</v>
+        <v>119839519</v>
       </c>
       <c r="B23" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2858,25 +2857,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2886,10 +2885,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547565</v>
+        <v>547233</v>
       </c>
       <c r="R23" t="n">
-        <v>6960801</v>
+        <v>6960631</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2948,10 +2947,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119839515</v>
+        <v>119839524</v>
       </c>
       <c r="B24" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2964,21 +2963,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2988,10 +2987,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547120</v>
+        <v>547492</v>
       </c>
       <c r="R24" t="n">
-        <v>6960622</v>
+        <v>6960705</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3050,10 +3049,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119839513</v>
+        <v>119839525</v>
       </c>
       <c r="B25" t="n">
-        <v>91832</v>
+        <v>91463</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3066,21 +3065,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3090,10 +3089,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547275</v>
+        <v>547520</v>
       </c>
       <c r="R25" t="n">
-        <v>6960558</v>
+        <v>6960746</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3152,10 +3151,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119839524</v>
+        <v>119839526</v>
       </c>
       <c r="B26" t="n">
-        <v>91856</v>
+        <v>91844</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3164,25 +3163,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2059</v>
+        <v>4365</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3192,10 +3191,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547492</v>
+        <v>547529</v>
       </c>
       <c r="R26" t="n">
-        <v>6960705</v>
+        <v>6960749</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3254,10 +3253,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119839518</v>
+        <v>119839530</v>
       </c>
       <c r="B27" t="n">
-        <v>91840</v>
+        <v>90087</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3266,25 +3265,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>256335</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3294,10 +3293,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>547209</v>
+        <v>547413</v>
       </c>
       <c r="R27" t="n">
-        <v>6960619</v>
+        <v>6960666</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3338,6 +3337,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119839519</v>
+        <v>119839529</v>
       </c>
       <c r="B28" t="n">
-        <v>91840</v>
+        <v>91310</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3368,25 +3368,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>547233</v>
+        <v>547537</v>
       </c>
       <c r="R28" t="n">
-        <v>6960631</v>
+        <v>6960720</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -1927,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119839528</v>
+        <v>119839516</v>
       </c>
       <c r="B14" t="n">
-        <v>91884</v>
+        <v>91310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,25 +1939,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>1958</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547565</v>
+        <v>547148</v>
       </c>
       <c r="R14" t="n">
-        <v>6960801</v>
+        <v>6960637</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2029,10 +2029,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119839516</v>
+        <v>119839512</v>
       </c>
       <c r="B15" t="n">
-        <v>91310</v>
+        <v>91825</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2041,25 +2041,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1958</v>
+        <v>1968</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547148</v>
+        <v>547281</v>
       </c>
       <c r="R15" t="n">
-        <v>6960637</v>
+        <v>6960553</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119839512</v>
+        <v>119839518</v>
       </c>
       <c r="B16" t="n">
-        <v>91825</v>
+        <v>91840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2143,25 +2143,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1968</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547281</v>
+        <v>547209</v>
       </c>
       <c r="R16" t="n">
-        <v>6960553</v>
+        <v>6960619</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2233,10 +2233,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119839518</v>
+        <v>119839528</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2245,25 +2245,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547209</v>
+        <v>547565</v>
       </c>
       <c r="R17" t="n">
-        <v>6960619</v>
+        <v>6960801</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -1723,10 +1723,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119839531</v>
+        <v>119839518</v>
       </c>
       <c r="B12" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1739,21 +1739,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547405</v>
+        <v>547209</v>
       </c>
       <c r="R12" t="n">
-        <v>6960663</v>
+        <v>6960619</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119839513</v>
+        <v>119839515</v>
       </c>
       <c r="B13" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1841,21 +1841,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547275</v>
+        <v>547120</v>
       </c>
       <c r="R13" t="n">
-        <v>6960558</v>
+        <v>6960622</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119839516</v>
+        <v>119839529</v>
       </c>
       <c r="B14" t="n">
         <v>91310</v>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547148</v>
+        <v>547537</v>
       </c>
       <c r="R14" t="n">
-        <v>6960637</v>
+        <v>6960720</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2029,10 +2029,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119839512</v>
+        <v>119839517</v>
       </c>
       <c r="B15" t="n">
-        <v>91825</v>
+        <v>91834</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2045,21 +2045,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1968</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547281</v>
+        <v>547152</v>
       </c>
       <c r="R15" t="n">
-        <v>6960553</v>
+        <v>6960633</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119839518</v>
+        <v>119839516</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>91310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2143,25 +2143,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547209</v>
+        <v>547148</v>
       </c>
       <c r="R16" t="n">
-        <v>6960619</v>
+        <v>6960637</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2233,10 +2233,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119839528</v>
+        <v>119839524</v>
       </c>
       <c r="B17" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2249,21 +2249,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547565</v>
+        <v>547492</v>
       </c>
       <c r="R17" t="n">
-        <v>6960801</v>
+        <v>6960705</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119839522</v>
+        <v>119839513</v>
       </c>
       <c r="B18" t="n">
-        <v>91883</v>
+        <v>91832</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2351,21 +2351,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547502</v>
+        <v>547275</v>
       </c>
       <c r="R18" t="n">
-        <v>6960695</v>
+        <v>6960558</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2437,10 +2437,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839517</v>
+        <v>119839530</v>
       </c>
       <c r="B19" t="n">
-        <v>91834</v>
+        <v>90087</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,25 +2449,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>256335</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547152</v>
+        <v>547413</v>
       </c>
       <c r="R19" t="n">
-        <v>6960633</v>
+        <v>6960666</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2521,6 +2521,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2539,10 +2540,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839527</v>
+        <v>119839519</v>
       </c>
       <c r="B20" t="n">
-        <v>91826</v>
+        <v>91840</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2551,25 +2552,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2579,10 +2580,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547533</v>
+        <v>547233</v>
       </c>
       <c r="R20" t="n">
-        <v>6960760</v>
+        <v>6960631</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2641,10 +2642,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119839514</v>
+        <v>119839512</v>
       </c>
       <c r="B21" t="n">
-        <v>91884</v>
+        <v>91825</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2657,21 +2658,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>1968</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,10 +2682,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547173</v>
+        <v>547281</v>
       </c>
       <c r="R21" t="n">
-        <v>6960564</v>
+        <v>6960553</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2743,10 +2744,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119839515</v>
+        <v>119839531</v>
       </c>
       <c r="B22" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2755,25 +2756,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2783,10 +2784,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547120</v>
+        <v>547405</v>
       </c>
       <c r="R22" t="n">
-        <v>6960622</v>
+        <v>6960663</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2845,10 +2846,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119839519</v>
+        <v>119839527</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>91826</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2857,25 +2858,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2885,10 +2886,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547233</v>
+        <v>547533</v>
       </c>
       <c r="R23" t="n">
-        <v>6960631</v>
+        <v>6960760</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2947,10 +2948,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119839524</v>
+        <v>119839528</v>
       </c>
       <c r="B24" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2963,21 +2964,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2987,10 +2988,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547492</v>
+        <v>547565</v>
       </c>
       <c r="R24" t="n">
-        <v>6960705</v>
+        <v>6960801</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3049,10 +3050,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119839525</v>
+        <v>119839526</v>
       </c>
       <c r="B25" t="n">
-        <v>91463</v>
+        <v>91844</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3061,25 +3062,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4745</v>
+        <v>4365</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3089,10 +3090,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547520</v>
+        <v>547529</v>
       </c>
       <c r="R25" t="n">
-        <v>6960746</v>
+        <v>6960749</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3151,10 +3152,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119839526</v>
+        <v>119839514</v>
       </c>
       <c r="B26" t="n">
-        <v>91844</v>
+        <v>91884</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3163,25 +3164,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3191,10 +3192,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547529</v>
+        <v>547173</v>
       </c>
       <c r="R26" t="n">
-        <v>6960749</v>
+        <v>6960564</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3253,10 +3254,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119839530</v>
+        <v>119839522</v>
       </c>
       <c r="B27" t="n">
-        <v>90087</v>
+        <v>91883</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3265,25 +3266,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>256335</v>
+        <v>5448</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3293,10 +3294,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>547413</v>
+        <v>547502</v>
       </c>
       <c r="R27" t="n">
-        <v>6960666</v>
+        <v>6960695</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3337,7 +3338,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119839529</v>
+        <v>119839525</v>
       </c>
       <c r="B28" t="n">
-        <v>91310</v>
+        <v>91463</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3368,25 +3368,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1958</v>
+        <v>4745</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>547537</v>
+        <v>547520</v>
       </c>
       <c r="R28" t="n">
-        <v>6960720</v>
+        <v>6960746</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2233,10 +2233,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119839524</v>
+        <v>119839530</v>
       </c>
       <c r="B17" t="n">
-        <v>91856</v>
+        <v>90087</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2245,25 +2245,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2059</v>
+        <v>256335</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547492</v>
+        <v>547413</v>
       </c>
       <c r="R17" t="n">
-        <v>6960705</v>
+        <v>6960666</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2317,6 +2317,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2335,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119839513</v>
+        <v>119839524</v>
       </c>
       <c r="B18" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2351,21 +2352,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2375,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547275</v>
+        <v>547492</v>
       </c>
       <c r="R18" t="n">
-        <v>6960558</v>
+        <v>6960705</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2437,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839530</v>
+        <v>119839513</v>
       </c>
       <c r="B19" t="n">
-        <v>90087</v>
+        <v>91832</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,25 +2450,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>256335</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2477,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547413</v>
+        <v>547275</v>
       </c>
       <c r="R19" t="n">
-        <v>6960666</v>
+        <v>6960558</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2521,7 +2522,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2131,10 +2131,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119839516</v>
+        <v>119839513</v>
       </c>
       <c r="B16" t="n">
-        <v>91310</v>
+        <v>91832</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2143,25 +2143,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1958</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547148</v>
+        <v>547275</v>
       </c>
       <c r="R16" t="n">
-        <v>6960637</v>
+        <v>6960558</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2233,10 +2233,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119839530</v>
+        <v>119839516</v>
       </c>
       <c r="B17" t="n">
-        <v>90087</v>
+        <v>91310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2249,21 +2249,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>256335</v>
+        <v>1958</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547413</v>
+        <v>547148</v>
       </c>
       <c r="R17" t="n">
-        <v>6960666</v>
+        <v>6960637</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2317,7 +2317,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2438,10 +2437,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839513</v>
+        <v>119839530</v>
       </c>
       <c r="B19" t="n">
-        <v>91832</v>
+        <v>90087</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,25 +2449,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>256335</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2478,10 +2477,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547275</v>
+        <v>547413</v>
       </c>
       <c r="R19" t="n">
-        <v>6960558</v>
+        <v>6960666</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2522,6 +2521,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2131,10 +2131,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119839513</v>
+        <v>119839516</v>
       </c>
       <c r="B16" t="n">
-        <v>91832</v>
+        <v>91310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2143,25 +2143,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>1958</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547275</v>
+        <v>547148</v>
       </c>
       <c r="R16" t="n">
-        <v>6960558</v>
+        <v>6960637</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2233,10 +2233,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119839516</v>
+        <v>119839530</v>
       </c>
       <c r="B17" t="n">
-        <v>91310</v>
+        <v>90087</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2249,21 +2249,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1958</v>
+        <v>256335</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547148</v>
+        <v>547413</v>
       </c>
       <c r="R17" t="n">
-        <v>6960637</v>
+        <v>6960666</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2317,6 +2317,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2437,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839530</v>
+        <v>119839513</v>
       </c>
       <c r="B19" t="n">
-        <v>90087</v>
+        <v>91832</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,25 +2450,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>256335</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2477,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547413</v>
+        <v>547275</v>
       </c>
       <c r="R19" t="n">
-        <v>6960666</v>
+        <v>6960558</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2521,7 +2522,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -1723,10 +1723,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119839518</v>
+        <v>119839526</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
+        <v>91862</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,25 +1735,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547209</v>
+        <v>547529</v>
       </c>
       <c r="R12" t="n">
-        <v>6960619</v>
+        <v>6960749</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119839515</v>
+        <v>119839514</v>
       </c>
       <c r="B13" t="n">
-        <v>91834</v>
+        <v>91902</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1841,21 +1841,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547120</v>
+        <v>547173</v>
       </c>
       <c r="R13" t="n">
-        <v>6960622</v>
+        <v>6960564</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1927,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119839529</v>
+        <v>119839512</v>
       </c>
       <c r="B14" t="n">
-        <v>91310</v>
+        <v>91843</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,25 +1939,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1958</v>
+        <v>1968</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547537</v>
+        <v>547281</v>
       </c>
       <c r="R14" t="n">
-        <v>6960720</v>
+        <v>6960553</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2029,10 +2029,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119839517</v>
+        <v>119839513</v>
       </c>
       <c r="B15" t="n">
-        <v>91834</v>
+        <v>91850</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2045,21 +2045,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547152</v>
+        <v>547275</v>
       </c>
       <c r="R15" t="n">
-        <v>6960633</v>
+        <v>6960558</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119839513</v>
+        <v>119839517</v>
       </c>
       <c r="B16" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547275</v>
+        <v>547152</v>
       </c>
       <c r="R16" t="n">
-        <v>6960558</v>
+        <v>6960633</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2233,10 +2233,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119839516</v>
+        <v>119839518</v>
       </c>
       <c r="B17" t="n">
-        <v>91310</v>
+        <v>91858</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2245,25 +2245,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547148</v>
+        <v>547209</v>
       </c>
       <c r="R17" t="n">
-        <v>6960637</v>
+        <v>6960619</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119839524</v>
+        <v>119839519</v>
       </c>
       <c r="B18" t="n">
-        <v>91856</v>
+        <v>91858</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2347,25 +2347,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547492</v>
+        <v>547233</v>
       </c>
       <c r="R18" t="n">
-        <v>6960705</v>
+        <v>6960631</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2437,10 +2437,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839530</v>
+        <v>119839515</v>
       </c>
       <c r="B19" t="n">
-        <v>90087</v>
+        <v>91852</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,25 +2449,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>256335</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547413</v>
+        <v>547120</v>
       </c>
       <c r="R19" t="n">
-        <v>6960666</v>
+        <v>6960622</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2521,7 +2521,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2540,10 +2539,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839519</v>
+        <v>119839524</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>91874</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,25 +2551,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2580,10 +2579,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547233</v>
+        <v>547492</v>
       </c>
       <c r="R20" t="n">
-        <v>6960631</v>
+        <v>6960705</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2642,10 +2641,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119839512</v>
+        <v>119839529</v>
       </c>
       <c r="B21" t="n">
-        <v>91825</v>
+        <v>91328</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2654,25 +2653,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1968</v>
+        <v>1958</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2682,10 +2681,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547281</v>
+        <v>547537</v>
       </c>
       <c r="R21" t="n">
-        <v>6960553</v>
+        <v>6960720</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2744,10 +2743,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119839531</v>
+        <v>119839527</v>
       </c>
       <c r="B22" t="n">
-        <v>91852</v>
+        <v>91844</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2756,25 +2755,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4366</v>
+        <v>3100</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2784,10 +2783,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547405</v>
+        <v>547533</v>
       </c>
       <c r="R22" t="n">
-        <v>6960663</v>
+        <v>6960760</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2846,10 +2845,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119839527</v>
+        <v>119839525</v>
       </c>
       <c r="B23" t="n">
-        <v>91826</v>
+        <v>91481</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2862,21 +2861,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3100</v>
+        <v>4745</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2886,10 +2885,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547533</v>
+        <v>547520</v>
       </c>
       <c r="R23" t="n">
-        <v>6960760</v>
+        <v>6960746</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2948,10 +2947,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119839528</v>
+        <v>119839531</v>
       </c>
       <c r="B24" t="n">
-        <v>91884</v>
+        <v>91870</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2960,25 +2959,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2988,10 +2987,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547565</v>
+        <v>547405</v>
       </c>
       <c r="R24" t="n">
-        <v>6960801</v>
+        <v>6960663</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3050,10 +3049,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119839526</v>
+        <v>119839528</v>
       </c>
       <c r="B25" t="n">
-        <v>91844</v>
+        <v>91902</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3062,25 +3061,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3090,10 +3089,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547529</v>
+        <v>547565</v>
       </c>
       <c r="R25" t="n">
-        <v>6960749</v>
+        <v>6960801</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3152,10 +3151,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119839514</v>
+        <v>119839522</v>
       </c>
       <c r="B26" t="n">
-        <v>91884</v>
+        <v>91901</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3168,21 +3167,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3192,10 +3191,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547173</v>
+        <v>547502</v>
       </c>
       <c r="R26" t="n">
-        <v>6960564</v>
+        <v>6960695</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3254,10 +3253,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119839522</v>
+        <v>119839530</v>
       </c>
       <c r="B27" t="n">
-        <v>91883</v>
+        <v>90104</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3266,25 +3265,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5448</v>
+        <v>256335</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3294,10 +3293,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>547502</v>
+        <v>547413</v>
       </c>
       <c r="R27" t="n">
-        <v>6960695</v>
+        <v>6960666</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3338,6 +3337,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119839525</v>
+        <v>119839516</v>
       </c>
       <c r="B28" t="n">
-        <v>91463</v>
+        <v>91328</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3368,25 +3368,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4745</v>
+        <v>1958</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>547520</v>
+        <v>547148</v>
       </c>
       <c r="R28" t="n">
-        <v>6960746</v>
+        <v>6960637</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -1723,10 +1723,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119839526</v>
+        <v>119839517</v>
       </c>
       <c r="B12" t="n">
-        <v>91862</v>
+        <v>91852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,25 +1735,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547529</v>
+        <v>547152</v>
       </c>
       <c r="R12" t="n">
-        <v>6960749</v>
+        <v>6960633</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119839514</v>
+        <v>119839529</v>
       </c>
       <c r="B13" t="n">
-        <v>91902</v>
+        <v>91328</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,25 +1837,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>1958</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547173</v>
+        <v>547537</v>
       </c>
       <c r="R13" t="n">
-        <v>6960564</v>
+        <v>6960720</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1927,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119839512</v>
+        <v>119839525</v>
       </c>
       <c r="B14" t="n">
-        <v>91843</v>
+        <v>91481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1943,21 +1943,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1968</v>
+        <v>4745</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547281</v>
+        <v>547520</v>
       </c>
       <c r="R14" t="n">
-        <v>6960553</v>
+        <v>6960746</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2029,10 +2029,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119839513</v>
+        <v>119839531</v>
       </c>
       <c r="B15" t="n">
-        <v>91850</v>
+        <v>91870</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2041,25 +2041,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547275</v>
+        <v>547405</v>
       </c>
       <c r="R15" t="n">
-        <v>6960558</v>
+        <v>6960663</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119839517</v>
+        <v>119839514</v>
       </c>
       <c r="B16" t="n">
-        <v>91852</v>
+        <v>91902</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547152</v>
+        <v>547173</v>
       </c>
       <c r="R16" t="n">
-        <v>6960633</v>
+        <v>6960564</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2233,10 +2233,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119839518</v>
+        <v>119839513</v>
       </c>
       <c r="B17" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2245,25 +2245,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547209</v>
+        <v>547275</v>
       </c>
       <c r="R17" t="n">
-        <v>6960619</v>
+        <v>6960558</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119839519</v>
+        <v>119839528</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2347,25 +2347,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547233</v>
+        <v>547565</v>
       </c>
       <c r="R18" t="n">
-        <v>6960631</v>
+        <v>6960801</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2437,10 +2437,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839515</v>
+        <v>119839524</v>
       </c>
       <c r="B19" t="n">
-        <v>91852</v>
+        <v>91874</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2453,21 +2453,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547120</v>
+        <v>547492</v>
       </c>
       <c r="R19" t="n">
-        <v>6960622</v>
+        <v>6960705</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839524</v>
+        <v>119839527</v>
       </c>
       <c r="B20" t="n">
-        <v>91874</v>
+        <v>91844</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2555,21 +2555,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2059</v>
+        <v>3100</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547492</v>
+        <v>547533</v>
       </c>
       <c r="R20" t="n">
-        <v>6960705</v>
+        <v>6960760</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2641,10 +2641,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119839529</v>
+        <v>119839526</v>
       </c>
       <c r="B21" t="n">
-        <v>91328</v>
+        <v>91862</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2657,21 +2657,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1958</v>
+        <v>4365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547537</v>
+        <v>547529</v>
       </c>
       <c r="R21" t="n">
-        <v>6960720</v>
+        <v>6960749</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2743,10 +2743,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119839527</v>
+        <v>119839522</v>
       </c>
       <c r="B22" t="n">
-        <v>91844</v>
+        <v>91901</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2759,21 +2759,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3100</v>
+        <v>5448</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2783,10 +2783,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547533</v>
+        <v>547502</v>
       </c>
       <c r="R22" t="n">
-        <v>6960760</v>
+        <v>6960695</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2845,10 +2845,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119839525</v>
+        <v>119839516</v>
       </c>
       <c r="B23" t="n">
-        <v>91481</v>
+        <v>91328</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2857,25 +2857,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4745</v>
+        <v>1958</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547520</v>
+        <v>547148</v>
       </c>
       <c r="R23" t="n">
-        <v>6960746</v>
+        <v>6960637</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2947,10 +2947,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119839531</v>
+        <v>119839518</v>
       </c>
       <c r="B24" t="n">
-        <v>91870</v>
+        <v>91858</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2963,21 +2963,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547405</v>
+        <v>547209</v>
       </c>
       <c r="R24" t="n">
-        <v>6960663</v>
+        <v>6960619</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3049,10 +3049,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119839528</v>
+        <v>119839515</v>
       </c>
       <c r="B25" t="n">
-        <v>91902</v>
+        <v>91852</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3065,21 +3065,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3089,10 +3089,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547565</v>
+        <v>547120</v>
       </c>
       <c r="R25" t="n">
-        <v>6960801</v>
+        <v>6960622</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3151,10 +3151,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119839522</v>
+        <v>119839512</v>
       </c>
       <c r="B26" t="n">
-        <v>91901</v>
+        <v>91843</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3167,21 +3167,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5448</v>
+        <v>1968</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547502</v>
+        <v>547281</v>
       </c>
       <c r="R26" t="n">
-        <v>6960695</v>
+        <v>6960553</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3253,10 +3253,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119839530</v>
+        <v>119839519</v>
       </c>
       <c r="B27" t="n">
-        <v>90104</v>
+        <v>91858</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3265,25 +3265,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>256335</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3293,10 +3293,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>547413</v>
+        <v>547233</v>
       </c>
       <c r="R27" t="n">
-        <v>6960666</v>
+        <v>6960631</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3337,7 +3337,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3356,10 +3355,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119839516</v>
+        <v>119839530</v>
       </c>
       <c r="B28" t="n">
-        <v>91328</v>
+        <v>90104</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3372,21 +3371,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1958</v>
+        <v>256335</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3396,10 +3395,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>547148</v>
+        <v>547413</v>
       </c>
       <c r="R28" t="n">
-        <v>6960637</v>
+        <v>6960666</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3440,6 +3439,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -1723,10 +1723,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119839517</v>
+        <v>119839518</v>
       </c>
       <c r="B12" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,25 +1735,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547152</v>
+        <v>547209</v>
       </c>
       <c r="R12" t="n">
-        <v>6960633</v>
+        <v>6960619</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119839529</v>
+        <v>119839514</v>
       </c>
       <c r="B13" t="n">
-        <v>91328</v>
+        <v>91902</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,25 +1837,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1958</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547537</v>
+        <v>547173</v>
       </c>
       <c r="R13" t="n">
-        <v>6960720</v>
+        <v>6960564</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1927,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119839525</v>
+        <v>119839512</v>
       </c>
       <c r="B14" t="n">
-        <v>91481</v>
+        <v>91843</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1943,21 +1943,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4745</v>
+        <v>1968</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547520</v>
+        <v>547281</v>
       </c>
       <c r="R14" t="n">
-        <v>6960746</v>
+        <v>6960553</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2029,10 +2029,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119839531</v>
+        <v>119839513</v>
       </c>
       <c r="B15" t="n">
-        <v>91870</v>
+        <v>91850</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2041,25 +2041,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547405</v>
+        <v>547275</v>
       </c>
       <c r="R15" t="n">
-        <v>6960663</v>
+        <v>6960558</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119839514</v>
+        <v>119839527</v>
       </c>
       <c r="B16" t="n">
-        <v>91902</v>
+        <v>91844</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>3100</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547173</v>
+        <v>547533</v>
       </c>
       <c r="R16" t="n">
-        <v>6960564</v>
+        <v>6960760</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2233,10 +2233,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119839513</v>
+        <v>119839517</v>
       </c>
       <c r="B17" t="n">
-        <v>91850</v>
+        <v>91852</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2249,21 +2249,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547275</v>
+        <v>547152</v>
       </c>
       <c r="R17" t="n">
-        <v>6960558</v>
+        <v>6960633</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119839528</v>
+        <v>119839522</v>
       </c>
       <c r="B18" t="n">
-        <v>91902</v>
+        <v>91901</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2351,21 +2351,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547565</v>
+        <v>547502</v>
       </c>
       <c r="R18" t="n">
-        <v>6960801</v>
+        <v>6960695</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2437,10 +2437,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839524</v>
+        <v>119839530</v>
       </c>
       <c r="B19" t="n">
-        <v>91874</v>
+        <v>90104</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,25 +2449,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2059</v>
+        <v>256335</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547492</v>
+        <v>547413</v>
       </c>
       <c r="R19" t="n">
-        <v>6960705</v>
+        <v>6960666</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2521,6 +2521,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2539,10 +2540,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839527</v>
+        <v>119839524</v>
       </c>
       <c r="B20" t="n">
-        <v>91844</v>
+        <v>91874</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2555,21 +2556,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3100</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2579,10 +2580,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547533</v>
+        <v>547492</v>
       </c>
       <c r="R20" t="n">
-        <v>6960760</v>
+        <v>6960705</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2641,10 +2642,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119839526</v>
+        <v>119839525</v>
       </c>
       <c r="B21" t="n">
-        <v>91862</v>
+        <v>91481</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2653,25 +2654,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4365</v>
+        <v>4745</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,10 +2682,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547529</v>
+        <v>547520</v>
       </c>
       <c r="R21" t="n">
-        <v>6960749</v>
+        <v>6960746</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2743,10 +2744,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119839522</v>
+        <v>119839515</v>
       </c>
       <c r="B22" t="n">
-        <v>91901</v>
+        <v>91852</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2759,21 +2760,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2783,10 +2784,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547502</v>
+        <v>547120</v>
       </c>
       <c r="R22" t="n">
-        <v>6960695</v>
+        <v>6960622</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2845,10 +2846,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119839516</v>
+        <v>119839531</v>
       </c>
       <c r="B23" t="n">
-        <v>91328</v>
+        <v>91870</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2857,25 +2858,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1958</v>
+        <v>4366</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2885,10 +2886,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547148</v>
+        <v>547405</v>
       </c>
       <c r="R23" t="n">
-        <v>6960637</v>
+        <v>6960663</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2947,10 +2948,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119839518</v>
+        <v>119839529</v>
       </c>
       <c r="B24" t="n">
-        <v>91858</v>
+        <v>91328</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2959,25 +2960,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2987,10 +2988,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547209</v>
+        <v>547537</v>
       </c>
       <c r="R24" t="n">
-        <v>6960619</v>
+        <v>6960720</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3049,10 +3050,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119839515</v>
+        <v>119839519</v>
       </c>
       <c r="B25" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3061,25 +3062,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3089,10 +3090,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547120</v>
+        <v>547233</v>
       </c>
       <c r="R25" t="n">
-        <v>6960622</v>
+        <v>6960631</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3151,10 +3152,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119839512</v>
+        <v>119839528</v>
       </c>
       <c r="B26" t="n">
-        <v>91843</v>
+        <v>91902</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3167,21 +3168,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1968</v>
+        <v>5449</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3191,10 +3192,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547281</v>
+        <v>547565</v>
       </c>
       <c r="R26" t="n">
-        <v>6960553</v>
+        <v>6960801</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3253,10 +3254,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119839519</v>
+        <v>119839526</v>
       </c>
       <c r="B27" t="n">
-        <v>91858</v>
+        <v>91862</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3265,25 +3266,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3293,10 +3294,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>547233</v>
+        <v>547529</v>
       </c>
       <c r="R27" t="n">
-        <v>6960631</v>
+        <v>6960749</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3355,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119839530</v>
+        <v>119839516</v>
       </c>
       <c r="B28" t="n">
-        <v>90104</v>
+        <v>91328</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3371,21 +3372,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>256335</v>
+        <v>1958</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3395,10 +3396,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>547413</v>
+        <v>547148</v>
       </c>
       <c r="R28" t="n">
-        <v>6960666</v>
+        <v>6960637</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3439,7 +3440,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2440,7 +2440,7 @@
         <v>119839530</v>
       </c>
       <c r="B19" t="n">
-        <v>90207</v>
+        <v>90217</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2440,7 +2440,7 @@
         <v>119839530</v>
       </c>
       <c r="B19" t="n">
-        <v>90217</v>
+        <v>90229</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2440,7 +2440,7 @@
         <v>119839530</v>
       </c>
       <c r="B19" t="n">
-        <v>90229</v>
+        <v>90455</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,28 +2449,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>256335</v>
+        <v>256703</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Våtflobäcken, Jmt</t>
@@ -2513,6 +2516,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ändrad från taggfingersvamp. Men någon taggfingersvamp har jag inte sett. I fältnoteringarna så står det tallfingersvamp. Slant nog vid reg i ap</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2440,7 +2440,7 @@
         <v>119839530</v>
       </c>
       <c r="B19" t="n">
-        <v>90455</v>
+        <v>90458</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2440,7 +2440,7 @@
         <v>119839530</v>
       </c>
       <c r="B19" t="n">
-        <v>90458</v>
+        <v>90460</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2440,7 +2440,7 @@
         <v>119839530</v>
       </c>
       <c r="B19" t="n">
-        <v>90460</v>
+        <v>90466</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2440,7 +2440,7 @@
         <v>119839530</v>
       </c>
       <c r="B19" t="n">
-        <v>90469</v>
+        <v>90486</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2440,7 +2440,7 @@
         <v>119839530</v>
       </c>
       <c r="B19" t="n">
-        <v>90486</v>
+        <v>90491</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2440,7 +2440,7 @@
         <v>119839530</v>
       </c>
       <c r="B19" t="n">
-        <v>90491</v>
+        <v>90493</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2440,12 +2440,7 @@
         <v>119839530</v>
       </c>
       <c r="B19" t="n">
-        <v>90493</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Dialog hos rapportör</t>
-        </is>
+        <v>91039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2440,7 +2440,7 @@
         <v>119839530</v>
       </c>
       <c r="B19" t="n">
-        <v>91039</v>
+        <v>91041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2440,7 +2440,7 @@
         <v>119839530</v>
       </c>
       <c r="B19" t="n">
-        <v>91041</v>
+        <v>91042</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2440,7 +2440,7 @@
         <v>119839530</v>
       </c>
       <c r="B19" t="n">
-        <v>91042</v>
+        <v>91045</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2440,7 +2440,7 @@
         <v>119839530</v>
       </c>
       <c r="B19" t="n">
-        <v>91045</v>
+        <v>91047</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2440,7 +2440,7 @@
         <v>119839530</v>
       </c>
       <c r="B19" t="n">
-        <v>91047</v>
+        <v>91051</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2440,7 +2440,7 @@
         <v>119839530</v>
       </c>
       <c r="B19" t="n">
-        <v>91051</v>
+        <v>91052</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2440,7 +2440,7 @@
         <v>119839530</v>
       </c>
       <c r="B19" t="n">
-        <v>91052</v>
+        <v>91055</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2440,7 +2440,7 @@
         <v>119839530</v>
       </c>
       <c r="B19" t="n">
-        <v>91055</v>
+        <v>91083</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2440,7 +2440,7 @@
         <v>119839530</v>
       </c>
       <c r="B19" t="n">
-        <v>91083</v>
+        <v>91089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2440,7 +2440,7 @@
         <v>119839530</v>
       </c>
       <c r="B19" t="n">
-        <v>91089</v>
+        <v>91090</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -2440,7 +2440,7 @@
         <v>119839530</v>
       </c>
       <c r="B19" t="n">
-        <v>91090</v>
+        <v>91095</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97365684</v>
+        <v>97365681</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547322.5034778927</v>
+        <v>547545</v>
       </c>
       <c r="R2" t="n">
-        <v>6960623.223305303</v>
+        <v>6960694</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-10-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,50 +776,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97365668</v>
+        <v>96790412</v>
       </c>
       <c r="B3" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>1958</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>Norr om Norr-Krången, nordsida bäck, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547440.70439804</v>
+        <v>547502</v>
       </c>
       <c r="R3" t="n">
-        <v>6960663.395121538</v>
+        <v>6960669</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,22 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,35 +866,35 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>200-årig tallskog med inslag avbjörk i brant, kalkpåverkad sydsida på sandig morän</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119033403</v>
+        <v>97365667</v>
       </c>
       <c r="B4" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,34 +902,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1958</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547255</v>
+        <v>547379</v>
       </c>
       <c r="R4" t="n">
-        <v>6960681</v>
+        <v>6960630</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,62 +976,61 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119033437</v>
+        <v>97365682</v>
       </c>
       <c r="B5" t="n">
-        <v>91822</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547244</v>
+        <v>547318</v>
       </c>
       <c r="R5" t="n">
-        <v>6960599</v>
+        <v>6960617</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,12 +1057,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,27 +1077,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119033402</v>
+        <v>119839516</v>
       </c>
       <c r="B6" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,37 +1104,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1958</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547317</v>
+        <v>547148</v>
       </c>
       <c r="R6" t="n">
-        <v>6960672</v>
+        <v>6960637</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1181,12 +1158,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1201,65 +1178,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119033436</v>
+        <v>119839529</v>
       </c>
       <c r="B7" t="n">
-        <v>91822</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547291</v>
+        <v>547537</v>
       </c>
       <c r="R7" t="n">
-        <v>6960671</v>
+        <v>6960720</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1283,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1303,62 +1275,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119033400</v>
+        <v>97365677</v>
       </c>
       <c r="B8" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547375</v>
+        <v>547393</v>
       </c>
       <c r="R8" t="n">
-        <v>6960680</v>
+        <v>6960633</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,12 +1352,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1405,65 +1372,64 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119033401</v>
+        <v>119839512</v>
       </c>
       <c r="B9" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547331</v>
+        <v>547281</v>
       </c>
       <c r="R9" t="n">
-        <v>6960675</v>
+        <v>6960553</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1487,12 +1453,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1507,65 +1473,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119033435</v>
+        <v>119839524</v>
       </c>
       <c r="B10" t="n">
-        <v>91822</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547444</v>
+        <v>547492</v>
       </c>
       <c r="R10" t="n">
-        <v>6960695</v>
+        <v>6960705</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1589,12 +1550,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1609,62 +1570,66 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119033399</v>
+        <v>96790415</v>
       </c>
       <c r="B11" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>3100</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norrkrången Albacken, Jmt</t>
+          <t>Norr om Norr-Krången, nordsida bäck, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547394</v>
+        <v>547389</v>
       </c>
       <c r="R11" t="n">
-        <v>6960687</v>
+        <v>6960623</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1691,12 +1656,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1707,53 +1672,57 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>130-årig tallskog med inslag av gammal tall i brant, kalkpåverkad sydsida på sandig morän</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119839518</v>
+        <v>119839527</v>
       </c>
       <c r="B12" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1763,10 +1732,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547209</v>
+        <v>547533</v>
       </c>
       <c r="R12" t="n">
-        <v>6960619</v>
+        <v>6960760</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1825,15 +1794,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119839514</v>
+        <v>119839513</v>
       </c>
       <c r="B13" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1841,21 +1805,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1865,10 +1829,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547173</v>
+        <v>547275</v>
       </c>
       <c r="R13" t="n">
-        <v>6960564</v>
+        <v>6960558</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1927,15 +1891,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119839512</v>
+        <v>119839515</v>
       </c>
       <c r="B14" t="n">
-        <v>91843</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1943,21 +1902,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1968</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1967,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547281</v>
+        <v>547120</v>
       </c>
       <c r="R14" t="n">
-        <v>6960553</v>
+        <v>6960622</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2029,15 +1988,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119839513</v>
+        <v>119839517</v>
       </c>
       <c r="B15" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2045,21 +1999,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2069,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547275</v>
+        <v>547152</v>
       </c>
       <c r="R15" t="n">
-        <v>6960558</v>
+        <v>6960633</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2131,15 +2085,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119839527</v>
+        <v>120663918</v>
       </c>
       <c r="B16" t="n">
-        <v>91844</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2147,34 +2096,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547533</v>
+        <v>547421</v>
       </c>
       <c r="R16" t="n">
-        <v>6960760</v>
+        <v>6960561</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2201,12 +2150,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2233,15 +2182,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119839517</v>
+        <v>97365684</v>
       </c>
       <c r="B17" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2249,21 +2193,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2273,13 +2217,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547152</v>
+        <v>547323</v>
       </c>
       <c r="R17" t="n">
-        <v>6960633</v>
+        <v>6960623</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2303,12 +2247,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2323,27 +2267,26 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119839522</v>
+        <v>119033435</v>
       </c>
       <c r="B18" t="n">
-        <v>91901</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2351,37 +2294,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>Norrkrången Albacken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547502</v>
+        <v>547444</v>
       </c>
       <c r="R18" t="n">
         <v>6960695</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2405,12 +2348,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2425,63 +2368,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839530</v>
+        <v>119033436</v>
       </c>
       <c r="B19" t="n">
-        <v>91095</v>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>Norrkrången Albacken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547413</v>
+        <v>547291</v>
       </c>
       <c r="R19" t="n">
-        <v>6960666</v>
+        <v>6960671</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2505,17 +2445,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>ändrad från taggfingersvamp. Men någon taggfingersvamp har jag inte sett. I fältnoteringarna så står det tallfingersvamp. Slant nog vid reg i ap</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2524,34 +2459,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839524</v>
+        <v>119033437</v>
       </c>
       <c r="B20" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2559,37 +2488,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>Norrkrången Albacken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547492</v>
+        <v>547244</v>
       </c>
       <c r="R20" t="n">
-        <v>6960705</v>
+        <v>6960599</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2613,12 +2542,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2633,27 +2562,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119839525</v>
+        <v>119839518</v>
       </c>
       <c r="B21" t="n">
-        <v>91481</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2661,21 +2585,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2685,10 +2609,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547520</v>
+        <v>547209</v>
       </c>
       <c r="R21" t="n">
-        <v>6960746</v>
+        <v>6960619</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2747,15 +2671,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119839515</v>
+        <v>119839519</v>
       </c>
       <c r="B22" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2763,21 +2682,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2787,10 +2706,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547120</v>
+        <v>547233</v>
       </c>
       <c r="R22" t="n">
-        <v>6960622</v>
+        <v>6960631</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2849,37 +2768,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119839531</v>
+        <v>119839521</v>
       </c>
       <c r="B23" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2889,10 +2803,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547405</v>
+        <v>547289</v>
       </c>
       <c r="R23" t="n">
-        <v>6960663</v>
+        <v>6960709</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2951,37 +2865,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119839529</v>
+        <v>119839532</v>
       </c>
       <c r="B24" t="n">
-        <v>91328</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2991,10 +2900,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547537</v>
+        <v>547390</v>
       </c>
       <c r="R24" t="n">
-        <v>6960720</v>
+        <v>6960634</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3053,37 +2962,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119839519</v>
+        <v>119839526</v>
       </c>
       <c r="B25" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3093,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547233</v>
+        <v>547529</v>
       </c>
       <c r="R25" t="n">
-        <v>6960631</v>
+        <v>6960749</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3155,15 +3059,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119839528</v>
+        <v>119839531</v>
       </c>
       <c r="B26" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3171,21 +3070,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3195,10 +3094,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547565</v>
+        <v>547405</v>
       </c>
       <c r="R26" t="n">
-        <v>6960801</v>
+        <v>6960663</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3257,37 +3156,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119839526</v>
+        <v>119839525</v>
       </c>
       <c r="B27" t="n">
-        <v>91862</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4365</v>
+        <v>4745</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3297,10 +3191,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>547529</v>
+        <v>547520</v>
       </c>
       <c r="R27" t="n">
-        <v>6960749</v>
+        <v>6960746</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3359,37 +3253,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119839516</v>
+        <v>119839522</v>
       </c>
       <c r="B28" t="n">
-        <v>91328</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1958</v>
+        <v>5448</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3399,10 +3288,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>547148</v>
+        <v>547502</v>
       </c>
       <c r="R28" t="n">
-        <v>6960637</v>
+        <v>6960695</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3458,6 +3347,1327 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>119839534</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Våtflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>547397</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6960618</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>97365668</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Våtflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>547441</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6960664</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>96790414</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Norr om Norr-Krången, nordsida bäck, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>547436</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6960651</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>120-årig tallskog i brant, kalkpåverkad sydsida på sandig morän</t>
+        </is>
+      </c>
+      <c r="AN31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov björkhögstubbe av gammalt träd</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>96790411</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Norr om Norr-Krången, nordsida bäck, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>547490</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6960655</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>200-årig tallskog med inslag avbjörk i brant, kalkpåverkad sydsida på sandig morän</t>
+        </is>
+      </c>
+      <c r="AN32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov tall, typiska spår</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>97365672</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Våtflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>547496</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6960665</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>119033399</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Norrkrången Albacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>547394</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6960687</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>119033400</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Norrkrången Albacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>547375</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6960680</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>119033401</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Norrkrången Albacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>547331</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6960675</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>119033402</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Norrkrången Albacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>547317</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6960672</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>119033403</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Norrkrången Albacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>547255</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6960681</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>97365679</v>
+      </c>
+      <c r="B39" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Våtflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>547372</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6960631</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>119839533</v>
+      </c>
+      <c r="B40" t="n">
+        <v>87189</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>249254</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Mospindling</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Cortinarius areni-silvae</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Brandrud) Brandrud</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Våtflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>547388</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6960630</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>119839530</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Våtflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>547413</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6960666</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>ändrad från taggfingersvamp. Men någon taggfingersvamp har jag inte sett. I fältnoteringarna så står det tallfingersvamp. Slant nog vid reg i ap</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30779-2024 artfynd.xlsx
+++ b/artfynd/A 30779-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365681</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790412</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365667</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365682</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839516</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839529</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1385,6 +1420,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365677</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1482,6 +1522,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839512</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1579,6 +1624,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839524</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1694,6 +1744,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790415</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1791,6 +1846,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839527</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1888,6 +1948,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839513</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839515</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2082,6 +2152,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839517</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2179,6 +2254,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120663918</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2280,6 +2360,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365684</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2377,6 +2462,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033435</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2474,6 +2564,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033436</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2571,6 +2666,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033437</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2668,6 +2768,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839518</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2765,6 +2870,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839519</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2862,6 +2972,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839521</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2959,6 +3074,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839532</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3056,6 +3176,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839526</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3153,6 +3278,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839531</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3250,6 +3380,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839525</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3347,6 +3482,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839522</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3444,6 +3584,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839534</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3545,6 +3690,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365668</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3659,6 +3809,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790414</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3773,6 +3928,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790411</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3879,6 +4039,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365672</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3976,6 +4141,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033399</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4073,6 +4243,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033400</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4170,6 +4345,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033401</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4267,6 +4447,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033402</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4364,6 +4549,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119033403</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4465,6 +4655,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365679</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4562,6 +4757,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839533</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4668,8 +4868,55 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839530</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>